--- a/output/pdf_financials_xlsx/CDPR.xlsx
+++ b/output/pdf_financials_xlsx/CDPR.xlsx
@@ -1273,10 +1273,10 @@
         <v>-0.024983</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.03993</v>
+        <v>-0.03993</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.045936</v>
+        <v>-0.045936</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-0.037656</v>
@@ -1285,13 +1285,13 @@
         <v>-0.32932</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>2.050689</v>
+        <v>-2.050689</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>4.756009</v>
+        <v>-4.756009</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.003771</v>
+        <v>-1.111411</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>0.730109</v>
@@ -1355,7 +1355,7 @@
         <v>0.09537</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>-30.767546</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-0.062795</v>
@@ -1573,10 +1573,10 @@
         <v>-0.024983</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.03993</v>
+        <v>-0.03993</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.045936</v>
+        <v>-0.045936</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-0.037656</v>
@@ -1585,25 +1585,25 @@
         <v>-0.32932</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2.050689</v>
+        <v>-2.050689</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>4.756009</v>
+        <v>-4.756009</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.057591</v>
+        <v>-1.057591</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.730109</v>
+        <v>-0.730109</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>15.383773</v>
+        <v>-15.383773</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>5.098365</v>
+        <v>-5.098365</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>7.445975</v>
+        <v>-7.445975</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>-2.102004</v>
@@ -1747,10 +1747,10 @@
         <v>-0.024983</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.03993</v>
+        <v>-0.03993</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.045936</v>
+        <v>-0.045936</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-0.037656</v>
@@ -1759,25 +1759,25 @@
         <v>-0.32932</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>2.050689</v>
+        <v>-2.050689</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>4.756009</v>
+        <v>-4.756009</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.057591</v>
+        <v>-1.057591</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.730109</v>
+        <v>-0.730109</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>15.383773</v>
+        <v>-15.383773</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>5.098365</v>
+        <v>-5.098365</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>7.445975</v>
+        <v>-7.445975</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>-2.102004</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-2.552</v>
+        <v>2.552</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1953,13 +1953,13 @@
         <v>6.5864</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>25.633612</v>
+        <v>-25.633612</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>52.844544</v>
+        <v>-52.844544</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>15.108443</v>
+        <v>-15.108443</v>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
@@ -1967,13 +1967,13 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>153.83773</v>
+        <v>-153.83773</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>254.91825</v>
+        <v>-254.91825</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>248.199167</v>
+        <v>-248.199167</v>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
@@ -2007,10 +2007,10 @@
         <v>-0.024983</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.03993</v>
+        <v>-0.03993</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.045936</v>
+        <v>-0.045936</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.037656</v>
@@ -2019,13 +2019,13 @@
         <v>-0.32932</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>2.050689</v>
+        <v>-2.050689</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>4.756009</v>
+        <v>-4.756009</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.003771</v>
+        <v>-1.111411</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>0.730109</v>
@@ -2123,10 +2123,10 @@
         <v>-0.024983</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.03993</v>
+        <v>-0.03993</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.045936</v>
+        <v>-0.045936</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.037656</v>
@@ -2135,13 +2135,13 @@
         <v>-0.32932</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2.052008</v>
+        <v>-2.04937</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4.756009</v>
+        <v>-4.756009</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.003771</v>
+        <v>-1.111411</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0.730109</v>
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-2723.193502581184</v>
+        <v>2719.692646609956</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-46147.96235202795</v>
+        <v>46147.96235202795</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-660.106403966803</v>
+        <v>730.8933198300692</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>695.0771134805789</v>
@@ -2253,10 +2253,10 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -2265,19 +2265,19 @@
         <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>5.361780724886453</v>
+        <v>-4.842493011136295</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>13.06243314354432</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>1.247028638267366</v>
@@ -2335,25 +2335,25 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>-2721.44307459557</v>
+        <v>2721.44307459557</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>-46147.96235202795</v>
+        <v>46147.96235202795</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-695.4998618984362</v>
+        <v>695.4998618984362</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>695.0771134805789</v>
+        <v>-695.0771134805789</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>112.9657584014199</v>
+        <v>-112.9657584014199</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>2108.740430072837</v>
+        <v>-2108.740430072837</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>2621.536029517905</v>
+        <v>-2621.536029517905</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>-29.51935227193254</v>
@@ -6234,10 +6234,10 @@
         <v>-1.748495</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>4.756009</v>
+        <v>-4.756009</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>1.057591</v>
+        <v>-1.057591</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>-0.730109</v>
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>0.005341</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.129139</v>
+        <v>0.13448</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0.006131</v>
@@ -7371,7 +7371,7 @@
         <v>0.145051</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>-0.298344</v>
+        <v>0.2</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>0</v>
@@ -55220,7 +55220,11 @@
           <t>Units issued as a payment of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr">
         <is>
           <t>-</t>
@@ -64920,7 +64924,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D563" t="inlineStr"/>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E563" s="5" t="n">
         <v>0.005341</v>
       </c>
@@ -76399,16 +76407,16 @@
         </is>
       </c>
       <c r="N677" s="5" t="n">
-        <v>0.730109</v>
+        <v>-0.730109</v>
       </c>
       <c r="O677" s="5" t="n">
-        <v>15.383773</v>
+        <v>-15.383773</v>
       </c>
       <c r="P677" s="5" t="n">
-        <v>5.098365</v>
+        <v>-5.098365</v>
       </c>
       <c r="Q677" s="5" t="n">
-        <v>7.445975</v>
+        <v>-7.445975</v>
       </c>
       <c r="R677" t="inlineStr">
         <is>
@@ -76688,16 +76696,16 @@
         </is>
       </c>
       <c r="N680" s="5" t="n">
-        <v>0.734573</v>
+        <v>-0.734573</v>
       </c>
       <c r="O680" s="5" t="n">
-        <v>15.329633</v>
+        <v>-15.329633</v>
       </c>
       <c r="P680" s="5" t="n">
-        <v>5.083945</v>
+        <v>-5.083945</v>
       </c>
       <c r="Q680" s="5" t="n">
-        <v>7.279857</v>
+        <v>-7.279857</v>
       </c>
       <c r="R680" t="inlineStr">
         <is>
@@ -82348,16 +82356,16 @@
         </is>
       </c>
       <c r="K737" s="5" t="n">
-        <v>2.050689</v>
+        <v>-2.050689</v>
       </c>
       <c r="L737" s="5" t="n">
-        <v>4.756009</v>
+        <v>-4.756009</v>
       </c>
       <c r="M737" s="5" t="n">
-        <v>1.057591</v>
+        <v>-1.057591</v>
       </c>
       <c r="N737" s="5" t="n">
-        <v>3.71923</v>
+        <v>-3.71923</v>
       </c>
       <c r="O737" t="inlineStr">
         <is>
@@ -89718,13 +89726,13 @@
         <v>-0.024983</v>
       </c>
       <c r="G811" s="5" t="n">
-        <v>0.03993</v>
+        <v>-0.03993</v>
       </c>
       <c r="H811" s="5" t="n">
-        <v>0.045936</v>
+        <v>-0.045936</v>
       </c>
       <c r="I811" s="5" t="n">
-        <v>0.037656</v>
+        <v>-0.037656</v>
       </c>
       <c r="J811" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CDPR.xlsx
+++ b/output/pdf_financials_xlsx/CDPR.xlsx
@@ -2384,19 +2384,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.033839</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.013821</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.013821</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.005864</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.025766</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.739471</v>
@@ -2429,10 +2429,10 @@
         <v>0.992301</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.136721</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>11.472112</v>
       </c>
     </row>
     <row r="35">
@@ -2500,19 +2500,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.033839</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.013821</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.013821</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.005864</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.025766</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.739471</v>
@@ -2545,10 +2545,10 @@
         <v>0.992301</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.136721</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>11.472112</v>
       </c>
     </row>
     <row r="37">
@@ -3196,19 +3196,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.526631</v>
+        <v>0.492792</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.506613</v>
+        <v>0.492792</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.506613</v>
+        <v>0.492792</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.005864</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.023654</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.019827</v>
@@ -3241,10 +3241,10 @@
         <v>5.452989</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>7.278073</v>
+        <v>7.141352</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>11.630137</v>
+        <v>0.158025</v>
       </c>
     </row>
     <row r="49">
@@ -7752,16 +7752,16 @@
         <v>0</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-9.3e-05</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.000347</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.002218</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.002676</v>
       </c>
       <c r="O124" s="3" t="n">
         <v>0</v>
@@ -7812,16 +7812,16 @@
         <v>0</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-9.3e-05</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000347</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.002218</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.002676</v>
       </c>
       <c r="O125" s="3" t="n">
         <v>0</v>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -32905,7 +32905,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -33620,7 +33620,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E251" s="5" t="n">
@@ -34527,7 +34527,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -47244,7 +47244,11 @@
           <t>Capital lease repayments</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CDPR.xlsx
+++ b/output/pdf_financials_xlsx/CDPR.xlsx
@@ -2074,37 +2074,37 @@
         <v>0</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.00118</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.001319</v>
+        <v>0.013822</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.013822</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.011397</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.000504</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.001922</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.081928</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.122397</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.385676</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>1.887505</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>2.275982</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>0</v>
@@ -2132,37 +2132,37 @@
         <v>-0.037656</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.32932</v>
+        <v>-0.32814</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.04937</v>
+        <v>-2.036867</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-4.756009</v>
+        <v>-4.742187</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.111411</v>
+        <v>-1.100014</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.730109</v>
+        <v>0.730613</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>15.383773</v>
+        <v>15.385695</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>5.03557</v>
+        <v>5.117498</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>7.412718</v>
+        <v>7.535115</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.459511</v>
+        <v>-1.073835</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-16.139593</v>
+        <v>-14.252088</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-4.686974</v>
+        <v>-2.410992</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>35.483537</v>
@@ -2205,34 +2205,34 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>2719.692646609956</v>
+        <v>2703.100075643969</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>46147.96235202795</v>
+        <v>46013.8463031244</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>730.8933198300692</v>
+        <v>723.3983506727519</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>695.0771134805789</v>
+        <v>695.5569306930693</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>112.9657584014199</v>
+        <v>112.9798719864063</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>2082.767720134175</v>
+        <v>2116.654051527672</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>2609.827096338076</v>
+        <v>2652.919927754365</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-20.49654489418695</v>
+        <v>-15.0803298409188</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-39.76121531667244</v>
+        <v>-35.11119144579194</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-25.03119437110631</v>
+        <v>-12.87611353917951</v>
       </c>
       <c r="R30" s="1" t="inlineStr">
         <is>
@@ -6288,37 +6288,37 @@
         <v>0</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.00118</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0.001319</v>
+        <v>0.013822</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.013822</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.011397</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.000504</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.001922</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.081928</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.122397</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.385676</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>1.887505</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>2.275982</v>
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -39050,7 +39050,11 @@
           <t>Depreciation of property, plant, and equipment</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
@@ -43052,7 +43056,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -43149,7 +43157,11 @@
           <t>Depreciation of property, plant, and equipment 13</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E346" t="inlineStr">
         <is>
           <t>-</t>
@@ -45739,7 +45751,11 @@
           <t>Depreciation of property, plant and equipment 10</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E372" t="inlineStr">
         <is>
           <t>-</t>
@@ -48949,7 +48965,11 @@
           <t>Depreciation of property and equipment 11</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -50533,7 +50553,11 @@
           <t>Depreciation of property and equipment 12</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
@@ -51230,7 +51254,11 @@
           <t>Depreciation of property and equipment 10</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -53523,7 +53551,11 @@
           <t>Proceeds from disposal of property and equipment 12</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
           <t>-</t>
@@ -54626,7 +54658,11 @@
           <t>Proceeds from disposal of property and equipment 11</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E461" t="inlineStr">
         <is>
           <t>-</t>
@@ -55329,7 +55365,11 @@
           <t>Depreciation - Property and equipment 14</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E468" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CDPR.xlsx
+++ b/output/pdf_financials_xlsx/CDPR.xlsx
@@ -1585,16 +1585,16 @@
         <v>-0.32932</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>-2.050689</v>
+        <v>-1.710304</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-4.756009</v>
+        <v>-3.651827</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-1.057591</v>
+        <v>-1.157767</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-0.730109</v>
+        <v>-3.720337</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-15.383773</v>
@@ -1608,14 +1608,20 @@
       <c r="O20" s="3" t="n">
         <v>-2.102004</v>
       </c>
-      <c r="P20" s="3" t="n">
-        <v>-0.253328</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>-24.622689</v>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v>-10.885403</v>
+      <c r="P20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1643,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0</v>
+        <v>-0.340385</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>-1.104182</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>0</v>
@@ -1667,13 +1673,13 @@
         <v>0</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0</v>
+        <v>-0.253328</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>0</v>
+        <v>-24.622689</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>0</v>
+        <v>-10.885403</v>
       </c>
     </row>
     <row r="22">
@@ -4555,10 +4561,10 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.116095</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.041479</v>
       </c>
       <c r="O70" s="3" t="n">
         <v>0</v>
@@ -4570,7 +4576,7 @@
         <v>0</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>0.005991</v>
       </c>
     </row>
     <row r="71">
@@ -4613,10 +4619,10 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.116095</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.041479</v>
       </c>
       <c r="O71" s="3" t="n">
         <v>0</v>
@@ -4628,7 +4634,7 @@
         <v>0</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>0.005991</v>
       </c>
     </row>
     <row r="72">
@@ -4845,10 +4851,10 @@
         <v>0.560512</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.884578</v>
+        <v>0.768483</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>2.920008</v>
+        <v>2.878529</v>
       </c>
       <c r="O75" s="3" t="n">
         <v>21.010844</v>
@@ -4860,7 +4866,7 @@
         <v>65.949026</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>5.47422</v>
+        <v>5.468229</v>
       </c>
     </row>
     <row r="76">
@@ -5159,12 +5165,10 @@
         </is>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.04495791493483405</v>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1339212368656588</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>-0.05431762170033445</v>
       </c>
       <c r="O80" s="1" t="inlineStr">
         <is>
@@ -5181,10 +5185,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R80" s="3" t="n">
+        <v>0.0008979375763269422</v>
       </c>
     </row>
     <row r="81">
@@ -6228,16 +6230,16 @@
         <v>-0.037656</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>-0.32932</v>
+        <v>-1.710304</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>-1.748495</v>
+        <v>-3.651827</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>-4.756009</v>
+        <v>-3.651827</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>-1.057591</v>
+        <v>-1.157767</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>-0.730109</v>
@@ -6333,16 +6335,16 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.009563</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001166</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.031397</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000464</v>
       </c>
       <c r="F101" s="3" t="n">
         <v>7.7e-05</v>
@@ -6633,16 +6635,16 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.13448</v>
+        <v>0.124917</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.006131</v>
+        <v>0.004965</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.007699</v>
+        <v>0.023698</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.014175</v>
+        <v>0.013711</v>
       </c>
       <c r="F106" s="3" t="n">
         <v>0.000334</v>
@@ -7197,10 +7199,10 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.072395</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.06951499999999999</v>
       </c>
       <c r="L115" s="3" t="n">
         <v>0</v>
@@ -7251,7 +7253,7 @@
         <v>0</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.263144</v>
       </c>
       <c r="I116" s="3" t="n">
         <v>0</v>
@@ -10294,7 +10296,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -20252,7 +20258,11 @@
           <t>Lease liabilities 17</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -22583,7 +22593,11 @@
           <t>Lease liabilities 18</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -39438,7 +39452,11 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -51860,7 +51878,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -53452,7 +53474,11 @@
           <t>Proceeds from disposal of marketable securities 11</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
           <t>-</t>
@@ -54557,7 +54583,11 @@
           <t>Proceeds from disposal of marketable securities 10</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E460" t="inlineStr">
         <is>
           <t>-</t>
@@ -54858,7 +54888,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E463" t="inlineStr">
         <is>
           <t>-</t>
@@ -57272,7 +57306,11 @@
           <t>Issuance of shares under private placement 18</t>
         </is>
       </c>
-      <c r="D487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E487" t="inlineStr">
         <is>
           <t>-</t>
@@ -57371,7 +57409,11 @@
           <t>Issuance of shares under flow-through private placement 18</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E488" t="inlineStr">
         <is>
           <t>-</t>
@@ -59205,7 +59247,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D506" t="inlineStr"/>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E506" t="inlineStr">
         <is>
           <t>-</t>
@@ -60124,7 +60170,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E515" t="inlineStr">
         <is>
           <t>-</t>
@@ -63186,7 +63236,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D545" t="inlineStr"/>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E545" t="inlineStr">
         <is>
           <t>-</t>
@@ -64869,7 +64923,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D562" t="inlineStr"/>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E562" s="5" t="n">
         <v>-0.009563</v>
       </c>
@@ -67489,7 +67547,7 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
@@ -71305,7 +71363,7 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
@@ -80075,7 +80133,11 @@
           <t>Income taxes recovery 19</t>
         </is>
       </c>
-      <c r="D714" t="inlineStr"/>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E714" t="inlineStr">
         <is>
           <t>-</t>
@@ -82170,7 +82232,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D735" t="inlineStr"/>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E735" t="inlineStr">
         <is>
           <t>-</t>
@@ -82202,16 +82268,16 @@
         </is>
       </c>
       <c r="K735" s="5" t="n">
-        <v>1.710304</v>
+        <v>-1.710304</v>
       </c>
       <c r="L735" s="5" t="n">
-        <v>3.651827</v>
+        <v>-3.651827</v>
       </c>
       <c r="M735" s="5" t="n">
-        <v>1.157767</v>
+        <v>-1.157767</v>
       </c>
       <c r="N735" s="5" t="n">
-        <v>3.720337</v>
+        <v>-3.720337</v>
       </c>
       <c r="O735" t="inlineStr">
         <is>
@@ -84641,7 +84707,11 @@
           <t>Net loss from continuing operations 5</t>
         </is>
       </c>
-      <c r="D760" t="inlineStr"/>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E760" t="inlineStr">
         <is>
           <t>-</t>
@@ -84678,10 +84748,10 @@
         </is>
       </c>
       <c r="L760" s="5" t="n">
-        <v>3.651827</v>
+        <v>-3.651827</v>
       </c>
       <c r="M760" s="5" t="n">
-        <v>1.157767</v>
+        <v>-1.157767</v>
       </c>
       <c r="N760" t="inlineStr">
         <is>
@@ -86433,7 +86503,11 @@
           <t>Net loss from discontinued operations 4</t>
         </is>
       </c>
-      <c r="D778" t="inlineStr"/>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E778" t="inlineStr">
         <is>
           <t>-</t>
@@ -86465,10 +86539,10 @@
         </is>
       </c>
       <c r="K778" s="5" t="n">
-        <v>0.340385</v>
+        <v>-0.340385</v>
       </c>
       <c r="L778" s="5" t="n">
-        <v>1.104182</v>
+        <v>-1.104182</v>
       </c>
       <c r="M778" t="inlineStr">
         <is>
